--- a/Excel/BattleLevelConfig@cs.xlsx
+++ b/Excel/BattleLevelConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BattleLevelConfig" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>1002</t>
+    <t>1002,1002,1002</t>
   </si>
   <si>
     <t>诅咒之地1</t>
@@ -846,7 +846,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
